--- a/artfynd/A 47936-2023 artfynd.xlsx
+++ b/artfynd/A 47936-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47936-2023 artfynd.xlsx
+++ b/artfynd/A 47936-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113142370</v>
+        <v>114458753</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 47936, Gökstad, Sm</t>
+          <t>Säverum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589649</v>
+        <v>589888</v>
       </c>
       <c r="R2" t="n">
-        <v>6422887</v>
+        <v>6422885</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,84 +755,70 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113142513</v>
+        <v>115342273</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 47936, Gökstad, Sm</t>
+          <t>Säverum, Säverum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589882</v>
+        <v>589845</v>
       </c>
       <c r="R3" t="n">
-        <v>6422828</v>
+        <v>6422997</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,22 +842,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,61 +873,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Louise Lundberg, Magnus Kasselstrand, Claes Siöstedt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113142471</v>
+        <v>115355710</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -977,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589770</v>
+        <v>589720</v>
       </c>
       <c r="R4" t="n">
-        <v>6422824</v>
+        <v>6422975</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,58 +980,52 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Louise Lundberg, Claes Siöstedt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113142482</v>
+        <v>113378008</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1102,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589823</v>
+        <v>589699</v>
       </c>
       <c r="R5" t="n">
-        <v>6422842</v>
+        <v>6422832</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,22 +1063,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,51 +1096,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113142505</v>
+        <v>113378018</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1227,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589866</v>
+        <v>589703</v>
       </c>
       <c r="R6" t="n">
-        <v>6422809</v>
+        <v>6422818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,22 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,51 +1205,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113142520</v>
+        <v>113379017</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589867</v>
+        <v>589897</v>
       </c>
       <c r="R7" t="n">
-        <v>6422845</v>
+        <v>6422893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,22 +1281,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,65 +1314,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113142432</v>
+        <v>114458963</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 47936, Gökstad, Sm</t>
+          <t>Säverum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589670</v>
+        <v>589674</v>
       </c>
       <c r="R8" t="n">
-        <v>6422890</v>
+        <v>6422792</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,22 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,70 +1394,63 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113142344</v>
+        <v>113379014</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1602,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589669</v>
+        <v>589883</v>
       </c>
       <c r="R9" t="n">
-        <v>6422872</v>
+        <v>6422945</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1632,22 +1488,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,51 +1521,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113142456</v>
+        <v>113142527</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1727,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589774</v>
+        <v>589867</v>
       </c>
       <c r="R10" t="n">
-        <v>6422819</v>
+        <v>6422845</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1800,47 +1640,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113142438</v>
+        <v>113378104</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1848,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589710</v>
+        <v>589869</v>
       </c>
       <c r="R11" t="n">
-        <v>6422855</v>
+        <v>6422869</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,22 +1716,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,37 +1749,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113142527</v>
+        <v>102801190</v>
       </c>
       <c r="B12" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6031</v>
+        <v>101479</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Läderbagge</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Osmoderma eremita</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1959,23 +1782,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 47936, Gökstad, Sm</t>
+          <t>Kalmar län, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589867</v>
+        <v>589540</v>
       </c>
       <c r="R12" t="n">
-        <v>6422845</v>
+        <v>6422877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2000,96 +1816,99 @@
           <t>Lofta</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9C60CDA0-E18B-49C6-A4EB-87C7EE811293</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2021-11-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Ek-släktet</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Ek-släktet</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Thomas Johansson, Petter Almgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113142491</v>
+        <v>113378033</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2097,13 +1916,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589822</v>
+        <v>589746</v>
       </c>
       <c r="R13" t="n">
-        <v>6422837</v>
+        <v>6422842</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,22 +1946,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2151,7 +1960,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2170,65 +1978,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113142357</v>
+        <v>114458334</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 47936, Gökstad, Sm</t>
+          <t>Säverum, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589653</v>
+        <v>589580</v>
       </c>
       <c r="R14" t="n">
-        <v>6422878</v>
+        <v>6422885</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2252,22 +2049,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2276,84 +2063,72 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113377998</v>
+        <v>114458459</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 47936, Gökstad, Sm</t>
+          <t>Säverum, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589681</v>
+        <v>589671</v>
       </c>
       <c r="R15" t="n">
-        <v>6422855</v>
+        <v>6422922</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2377,12 +2152,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2024-01-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2391,34 +2166,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113379019</v>
+        <v>113142344</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2212,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2458,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589897</v>
+        <v>589669</v>
       </c>
       <c r="R16" t="n">
-        <v>6422893</v>
+        <v>6422872</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2488,12 +2261,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2521,15 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113379027</v>
+        <v>113142357</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2554,7 +2332,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2569,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589914</v>
+        <v>589653</v>
       </c>
       <c r="R17" t="n">
-        <v>6422864</v>
+        <v>6422878</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2599,12 +2381,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2632,15 +2424,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113378027</v>
+        <v>113142370</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2454,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2684,10 +2471,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589746</v>
+        <v>589649</v>
       </c>
       <c r="R18" t="n">
-        <v>6422842</v>
+        <v>6422887</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2714,12 +2501,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2747,15 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113378118</v>
+        <v>113142432</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2782,7 +2574,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2799,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589867</v>
+        <v>589670</v>
       </c>
       <c r="R19" t="n">
-        <v>6422870</v>
+        <v>6422890</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2829,12 +2621,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2862,50 +2664,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113378008</v>
+        <v>113142438</v>
       </c>
       <c r="B20" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2913,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589699</v>
+        <v>589710</v>
       </c>
       <c r="R20" t="n">
-        <v>6422832</v>
+        <v>6422855</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2943,12 +2737,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,15 +2780,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113378088</v>
+        <v>113142456</v>
       </c>
       <c r="B21" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3028,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589870</v>
+        <v>589774</v>
       </c>
       <c r="R21" t="n">
-        <v>6422833</v>
+        <v>6422819</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3058,12 +2857,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3091,15 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113379023</v>
+        <v>113142471</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +2928,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3139,10 +2947,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589914</v>
+        <v>589770</v>
       </c>
       <c r="R22" t="n">
-        <v>6422888</v>
+        <v>6422824</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3169,12 +2977,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3202,50 +3020,46 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113378018</v>
+        <v>113142482</v>
       </c>
       <c r="B23" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3253,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589703</v>
+        <v>589823</v>
       </c>
       <c r="R23" t="n">
-        <v>6422818</v>
+        <v>6422842</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3283,12 +3097,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3316,15 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113379021</v>
+        <v>113142491</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3349,7 +3168,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3364,10 +3187,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589900</v>
+        <v>589822</v>
       </c>
       <c r="R24" t="n">
-        <v>6422854</v>
+        <v>6422837</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3394,12 +3217,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,15 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113377953</v>
+        <v>113142505</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3460,7 +3288,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -3475,10 +3307,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589627</v>
+        <v>589866</v>
       </c>
       <c r="R25" t="n">
-        <v>6422874</v>
+        <v>6422809</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3505,12 +3337,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3538,15 +3380,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113378127</v>
+        <v>113142513</v>
       </c>
       <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3573,7 +3410,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3590,10 +3427,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589883</v>
+        <v>589882</v>
       </c>
       <c r="R26" t="n">
-        <v>6422867</v>
+        <v>6422828</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3620,12 +3457,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3653,15 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113377983</v>
+        <v>113142520</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3688,7 +3530,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3705,10 +3547,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589683</v>
+        <v>589867</v>
       </c>
       <c r="R27" t="n">
-        <v>6422826</v>
+        <v>6422845</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3735,12 +3577,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-11-23</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3768,15 +3620,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113378081</v>
+        <v>113377953</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3816,10 +3663,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589839</v>
+        <v>589627</v>
       </c>
       <c r="R28" t="n">
-        <v>6422835</v>
+        <v>6422874</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3879,15 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113379035</v>
+        <v>113377969</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3927,10 +3769,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589845</v>
+        <v>589658</v>
       </c>
       <c r="R29" t="n">
-        <v>6422804</v>
+        <v>6422885</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3990,50 +3832,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113378104</v>
+        <v>113377975</v>
       </c>
       <c r="B30" t="n">
-        <v>90954</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4041,10 +3875,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589869</v>
+        <v>589662</v>
       </c>
       <c r="R30" t="n">
-        <v>6422869</v>
+        <v>6422860</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4104,15 +3938,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113379029</v>
+        <v>113377983</v>
       </c>
       <c r="B31" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4137,7 +3966,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4152,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589913</v>
+        <v>589683</v>
       </c>
       <c r="R31" t="n">
-        <v>6422841</v>
+        <v>6422826</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4215,15 +4048,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113378097</v>
+        <v>113377989</v>
       </c>
       <c r="B32" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4250,7 +4078,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4267,10 +4095,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589842</v>
+        <v>589682</v>
       </c>
       <c r="R32" t="n">
-        <v>6422863</v>
+        <v>6422839</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4330,15 +4158,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113378091</v>
+        <v>113377998</v>
       </c>
       <c r="B33" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4365,7 +4188,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4382,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589870</v>
+        <v>589681</v>
       </c>
       <c r="R33" t="n">
-        <v>6422828</v>
+        <v>6422855</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4445,50 +4268,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113379017</v>
+        <v>113378027</v>
       </c>
       <c r="B34" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4496,10 +4315,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589897</v>
+        <v>589746</v>
       </c>
       <c r="R34" t="n">
-        <v>6422893</v>
+        <v>6422842</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4559,15 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113377975</v>
+        <v>113378042</v>
       </c>
       <c r="B35" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4592,7 +4406,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -4607,10 +4425,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589662</v>
+        <v>589740</v>
       </c>
       <c r="R35" t="n">
-        <v>6422860</v>
+        <v>6422846</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4670,15 +4488,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113378042</v>
+        <v>113378051</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4518,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4722,10 +4535,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589740</v>
+        <v>589808</v>
       </c>
       <c r="R36" t="n">
-        <v>6422846</v>
+        <v>6422756</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4788,12 +4601,7 @@
         <v>113378067</v>
       </c>
       <c r="B37" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4900,15 +4708,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113379032</v>
+        <v>113378081</v>
       </c>
       <c r="B38" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4948,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589871</v>
+        <v>589839</v>
       </c>
       <c r="R38" t="n">
-        <v>6422809</v>
+        <v>6422835</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5011,15 +4814,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113377989</v>
+        <v>113378088</v>
       </c>
       <c r="B39" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5046,7 +4844,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5063,10 +4861,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589682</v>
+        <v>589870</v>
       </c>
       <c r="R39" t="n">
-        <v>6422839</v>
+        <v>6422833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5126,15 +4924,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113379009</v>
+        <v>113378091</v>
       </c>
       <c r="B40" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5161,7 +4954,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5178,10 +4971,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589887</v>
+        <v>589870</v>
       </c>
       <c r="R40" t="n">
-        <v>6422866</v>
+        <v>6422828</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5241,51 +5034,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113378033</v>
+        <v>113378097</v>
       </c>
       <c r="B41" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5293,13 +5081,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589746</v>
+        <v>589842</v>
       </c>
       <c r="R41" t="n">
-        <v>6422842</v>
+        <v>6422863</v>
       </c>
       <c r="S41" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5337,6 +5125,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5355,15 +5144,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113377969</v>
+        <v>113378118</v>
       </c>
       <c r="B42" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5388,7 +5172,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -5403,10 +5191,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589658</v>
+        <v>589867</v>
       </c>
       <c r="R42" t="n">
-        <v>6422885</v>
+        <v>6422870</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5466,15 +5254,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113379025</v>
+        <v>113378127</v>
       </c>
       <c r="B43" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5501,10 +5284,14 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5514,10 +5301,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589903</v>
+        <v>589883</v>
       </c>
       <c r="R43" t="n">
-        <v>6422880</v>
+        <v>6422867</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5577,59 +5364,60 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>114458459</v>
+        <v>113379009</v>
       </c>
       <c r="B44" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Säverum, Sm</t>
+          <t>A 47936, Gökstad, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589671</v>
+        <v>589887</v>
       </c>
       <c r="R44" t="n">
-        <v>6422922</v>
+        <v>6422866</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5653,12 +5441,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,77 +5455,75 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>114458334</v>
+        <v>113379019</v>
       </c>
       <c r="B45" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Säverum, Sm</t>
+          <t>A 47936, Gökstad, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589580</v>
+        <v>589897</v>
       </c>
       <c r="R45" t="n">
-        <v>6422885</v>
+        <v>6422893</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5761,12 +5547,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5775,72 +5561,75 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>114458753</v>
+        <v>113379021</v>
       </c>
       <c r="B46" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Säverum, Sm</t>
+          <t>A 47936, Gökstad, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589888</v>
+        <v>589900</v>
       </c>
       <c r="R46" t="n">
-        <v>6422885</v>
+        <v>6422854</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5864,12 +5653,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5878,33 +5667,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115344740</v>
+        <v>113379023</v>
       </c>
       <c r="B47" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5929,11 +5714,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -5944,17 +5725,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Säverum (Säverum), Sm</t>
+          <t>A 47936, Gökstad, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589708</v>
+        <v>589914</v>
       </c>
       <c r="R47" t="n">
-        <v>6422965</v>
+        <v>6422888</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5978,22 +5759,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6009,61 +5780,52 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Louise Lundberg, Magnus Kasselstrand, Claes Siöstedt</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115355811</v>
+        <v>113379025</v>
       </c>
       <c r="B48" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -6073,10 +5835,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589744</v>
+        <v>589903</v>
       </c>
       <c r="R48" t="n">
-        <v>6422960</v>
+        <v>6422880</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6103,12 +5865,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6129,48 +5891,47 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Louise Lundberg, Claes Siöstedt</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>115355710</v>
+        <v>113379027</v>
       </c>
       <c r="B49" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -6180,10 +5941,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589720</v>
+        <v>589914</v>
       </c>
       <c r="R49" t="n">
-        <v>6422975</v>
+        <v>6422864</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6210,12 +5971,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6236,22 +5997,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Louise Lundberg, Claes Siöstedt</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>115345013</v>
+        <v>113379029</v>
       </c>
       <c r="B50" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6276,11 +6032,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -6291,17 +6043,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Säverum (Säverum), Sm</t>
+          <t>A 47936, Gökstad, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589720</v>
+        <v>589913</v>
       </c>
       <c r="R50" t="n">
-        <v>6422973</v>
+        <v>6422841</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6325,22 +6077,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6356,15 +6098,675 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>113379032</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>A 47936, Gökstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>589871</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6422809</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>113379035</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>A 47936, Gökstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>589845</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6422804</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>115344740</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Säverum, Säverum, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>589708</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6422965</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
           <t>Louise Lundberg</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
+      <c r="AX53" t="inlineStr">
         <is>
           <t>Louise Lundberg, Magnus Kasselstrand, Claes Siöstedt</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>115345013</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Säverum, Säverum, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>589720</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6422973</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Louise Lundberg, Magnus Kasselstrand, Claes Siöstedt</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>115355811</v>
+      </c>
+      <c r="B55" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>A 47936, Gökstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>589744</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6422960</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Louise Lundberg, Claes Siöstedt</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>114459139</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Säverum, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>589625</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6422812</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-01-30</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-01-30</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
